--- a/research/traditional_assets/database/data/norway/norway_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_coal_related_energy.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.516</v>
+        <v>-9.19</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,52 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.4744186046511628</v>
+      </c>
+      <c r="W2">
+        <v>-0.8354545454545454</v>
       </c>
       <c r="X2">
-        <v>0.05883665132962446</v>
+        <v>0.1197738582771159</v>
+      </c>
+      <c r="Y2">
+        <v>-0.9552284037316614</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>-9.558390578999017</v>
       </c>
       <c r="AB2">
-        <v>0.05875101196076347</v>
+        <v>0.1190182345917937</v>
+      </c>
+      <c r="AC2">
+        <v>-9.677408813590811</v>
       </c>
       <c r="AD2">
-        <v>0.279</v>
+        <v>1.01</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.279</v>
+        <v>1.01</v>
       </c>
       <c r="AG2">
-        <v>0.279</v>
+        <v>-39.79</v>
       </c>
       <c r="AH2">
-        <v>0.002471673207593973</v>
+        <v>0.01160786116538329</v>
       </c>
       <c r="AI2">
-        <v>0.01790872328134026</v>
+        <v>0.02462813947817605</v>
       </c>
       <c r="AJ2">
-        <v>0.002471673207593973</v>
+        <v>-0.8610690326769097</v>
       </c>
       <c r="AK2">
-        <v>0.01790872328134026</v>
+        <v>-189.4761904761897</v>
       </c>
       <c r="AL2">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="AM2">
-        <v>0.008</v>
+        <v>-0.602</v>
+      </c>
+      <c r="AN2">
+        <v>-0.1043388429752066</v>
       </c>
       <c r="AO2">
-        <v>-196.25</v>
+        <v>-389.6</v>
+      </c>
+      <c r="AP2">
+        <v>4.110537190082645</v>
       </c>
       <c r="AQ2">
-        <v>-196.25</v>
+        <v>16.17940199335548</v>
       </c>
     </row>
     <row r="3">
@@ -677,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.516</v>
+        <v>-9.19</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -701,52 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.4744186046511628</v>
+      </c>
+      <c r="W3">
+        <v>-0.8354545454545454</v>
       </c>
       <c r="X3">
-        <v>0.05883665132962446</v>
+        <v>0.1197738582771159</v>
+      </c>
+      <c r="Y3">
+        <v>-0.9552284037316614</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>-9.558390578999017</v>
       </c>
       <c r="AB3">
-        <v>0.05875101196076347</v>
+        <v>0.1190182345917937</v>
+      </c>
+      <c r="AC3">
+        <v>-9.677408813590811</v>
       </c>
       <c r="AD3">
-        <v>0.279</v>
+        <v>1.01</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.279</v>
+        <v>1.01</v>
       </c>
       <c r="AG3">
-        <v>0.279</v>
+        <v>-39.79</v>
       </c>
       <c r="AH3">
-        <v>0.002471673207593973</v>
+        <v>0.01160786116538329</v>
       </c>
       <c r="AI3">
-        <v>0.01790872328134026</v>
+        <v>0.02462813947817605</v>
       </c>
       <c r="AJ3">
-        <v>0.002471673207593973</v>
+        <v>-0.8610690326769097</v>
       </c>
       <c r="AK3">
-        <v>0.01790872328134026</v>
+        <v>-189.4761904761897</v>
       </c>
       <c r="AL3">
-        <v>0.008</v>
+        <v>0.025</v>
       </c>
       <c r="AM3">
-        <v>0.008</v>
+        <v>-0.602</v>
+      </c>
+      <c r="AN3">
+        <v>-0.1043388429752066</v>
       </c>
       <c r="AO3">
-        <v>-196.25</v>
+        <v>-389.6</v>
+      </c>
+      <c r="AP3">
+        <v>4.110537190082645</v>
       </c>
       <c r="AQ3">
-        <v>-196.25</v>
+        <v>16.17940199335548</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_coal_related_energy.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-9.19</v>
+        <v>-21.2</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>40.8</v>
+        <v>22.7</v>
       </c>
       <c r="V2">
-        <v>0.4744186046511628</v>
+        <v>1.94017094017094</v>
       </c>
       <c r="W2">
-        <v>-0.8354545454545454</v>
+        <v>-0.53</v>
       </c>
       <c r="X2">
-        <v>0.1197738582771159</v>
+        <v>0.09012200212892467</v>
       </c>
       <c r="Y2">
-        <v>-0.9552284037316614</v>
+        <v>-0.6201220021289247</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-9.558390578999017</v>
+        <v>-106.1904761904758</v>
       </c>
       <c r="AB2">
-        <v>0.1190182345917937</v>
+        <v>0.08837261001634555</v>
       </c>
       <c r="AC2">
-        <v>-9.677408813590811</v>
+        <v>-106.2788488004921</v>
       </c>
       <c r="AD2">
-        <v>1.01</v>
+        <v>0.439</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.01</v>
+        <v>0.439</v>
       </c>
       <c r="AG2">
-        <v>-39.79</v>
+        <v>-22.261</v>
       </c>
       <c r="AH2">
-        <v>0.01160786116538329</v>
+        <v>0.03616442870088146</v>
       </c>
       <c r="AI2">
-        <v>0.02462813947817605</v>
+        <v>0.02179850042206664</v>
       </c>
       <c r="AJ2">
-        <v>-0.8610690326769097</v>
+        <v>2.107849635451188</v>
       </c>
       <c r="AK2">
-        <v>-189.4761904761897</v>
+        <v>8.692307692307692</v>
       </c>
       <c r="AL2">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="AM2">
-        <v>-0.602</v>
+        <v>-1.205</v>
       </c>
       <c r="AN2">
-        <v>-0.1043388429752066</v>
+        <v>-0.01968609865470852</v>
       </c>
       <c r="AO2">
-        <v>-389.6</v>
+        <v>-495.5555555555556</v>
       </c>
       <c r="AP2">
-        <v>4.110537190082645</v>
+        <v>0.9982511210762331</v>
       </c>
       <c r="AQ2">
-        <v>16.17940199335548</v>
+        <v>18.50622406639004</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-9.19</v>
+        <v>-21.2</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>40.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3">
-        <v>0.4744186046511628</v>
+        <v>1.94017094017094</v>
       </c>
       <c r="W3">
-        <v>-0.8354545454545454</v>
+        <v>-0.53</v>
       </c>
       <c r="X3">
-        <v>0.1197738582771159</v>
+        <v>0.09012200212892467</v>
       </c>
       <c r="Y3">
-        <v>-0.9552284037316614</v>
+        <v>-0.6201220021289247</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-9.558390578999017</v>
+        <v>-106.1904761904758</v>
       </c>
       <c r="AB3">
-        <v>0.1190182345917937</v>
+        <v>0.08837261001634555</v>
       </c>
       <c r="AC3">
-        <v>-9.677408813590811</v>
+        <v>-106.2788488004921</v>
       </c>
       <c r="AD3">
-        <v>1.01</v>
+        <v>0.439</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.01</v>
+        <v>0.439</v>
       </c>
       <c r="AG3">
-        <v>-39.79</v>
+        <v>-22.261</v>
       </c>
       <c r="AH3">
-        <v>0.01160786116538329</v>
+        <v>0.03616442870088146</v>
       </c>
       <c r="AI3">
-        <v>0.02462813947817605</v>
+        <v>0.02179850042206664</v>
       </c>
       <c r="AJ3">
-        <v>-0.8610690326769097</v>
+        <v>2.107849635451188</v>
       </c>
       <c r="AK3">
-        <v>-189.4761904761897</v>
+        <v>8.692307692307692</v>
       </c>
       <c r="AL3">
-        <v>0.025</v>
+        <v>0.045</v>
       </c>
       <c r="AM3">
-        <v>-0.602</v>
+        <v>-1.205</v>
       </c>
       <c r="AN3">
-        <v>-0.1043388429752066</v>
+        <v>-0.01968609865470852</v>
       </c>
       <c r="AO3">
-        <v>-389.6</v>
+        <v>-495.5555555555556</v>
       </c>
       <c r="AP3">
-        <v>4.110537190082645</v>
+        <v>0.9982511210762331</v>
       </c>
       <c r="AQ3">
-        <v>16.17940199335548</v>
+        <v>18.50622406639004</v>
       </c>
     </row>
   </sheetData>
